--- a/Datas/W-物品配置表.xlsx
+++ b/Datas/W-物品配置表.xlsx
@@ -100,12 +100,81 @@
         </r>
       </text>
     </comment>
+    <comment ref="F2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>杨宗水:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+序号
+与item一一对应</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>杨宗水:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+序号
+与item一一对应</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>杨宗水:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+序号
+与item一一对应</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="57">
   <si>
     <t>##comment</t>
   </si>
@@ -122,6 +191,15 @@
     <t>细分类型</t>
   </si>
   <si>
+    <t>品质</t>
+  </si>
+  <si>
+    <t>图片</t>
+  </si>
+  <si>
+    <t>物品占据格子</t>
+  </si>
+  <si>
     <t>##var</t>
   </si>
   <si>
@@ -134,7 +212,13 @@
     <t>sub_type</t>
   </si>
   <si>
-    <t>index</t>
+    <t>quality</t>
+  </si>
+  <si>
+    <t>icon</t>
+  </si>
+  <si>
+    <t>bag_size</t>
   </si>
   <si>
     <t>##type</t>
@@ -149,6 +233,9 @@
     <t>ESubType</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -158,6 +245,9 @@
     <t>##</t>
   </si>
   <si>
+    <t>icon_1</t>
+  </si>
+  <si>
     <t>1级旧头盔</t>
   </si>
   <si>
@@ -255,9 +345,6 @@
   </si>
   <si>
     <t>仓库钥匙卡</t>
-  </si>
-  <si>
-    <t>测试物品</t>
   </si>
 </sst>
 </file>
@@ -443,12 +530,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -905,7 +992,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -924,6 +1011,9 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1258,7 +1348,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="11" style="1"/>
@@ -1266,19 +1356,18 @@
     <col min="3" max="3" width="13.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="16.5" style="1" customWidth="1"/>
     <col min="5" max="5" width="19.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11" style="1"/>
-    <col min="9" max="9" width="14.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.625" style="1" customWidth="1"/>
-    <col min="12" max="16" width="11" style="1"/>
-    <col min="17" max="17" width="12.25" style="1" customWidth="1"/>
-    <col min="18" max="18" width="12.75" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="11" style="1"/>
+    <col min="6" max="6" width="15.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.625" style="1" customWidth="1"/>
+    <col min="11" max="15" width="11" style="1"/>
+    <col min="16" max="16" width="12.25" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.75" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:5">
+    <row r="1" s="1" customFormat="1" spans="1:8">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1294,64 +1383,91 @@
       <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:6">
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="6" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:6">
+        <v>18</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="6" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:6">
+        <v>21</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:8">
       <c r="A5" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="7"/>
@@ -1361,16 +1477,22 @@
       <c r="E5" s="6">
         <v>0</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="2:14">
+      <c r="G5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="2:13">
       <c r="B6" s="8">
         <v>1001</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D6" s="9">
         <v>1</v>
@@ -1378,22 +1500,25 @@
       <c r="E6" s="9">
         <v>101</v>
       </c>
-      <c r="F6" s="3"/>
+      <c r="F6" s="10">
+        <v>2</v>
+      </c>
       <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="H6" s="10">
+        <v>2</v>
+      </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="2:14">
+    </row>
+    <row r="7" s="2" customFormat="1" spans="2:13">
       <c r="B7" s="8">
         <v>1002</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D7" s="9">
         <v>1</v>
@@ -1401,22 +1526,25 @@
       <c r="E7" s="9">
         <v>102</v>
       </c>
-      <c r="F7" s="3"/>
+      <c r="F7" s="10">
+        <v>2</v>
+      </c>
       <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+      <c r="H7" s="10">
+        <v>3</v>
+      </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="2:14">
+    </row>
+    <row r="8" s="1" customFormat="1" spans="2:13">
       <c r="B8" s="8">
         <v>1003</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D8" s="9">
         <v>1</v>
@@ -1424,22 +1552,25 @@
       <c r="E8" s="9">
         <v>103</v>
       </c>
-      <c r="F8" s="3"/>
+      <c r="F8" s="10">
+        <v>2</v>
+      </c>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="H8" s="10">
+        <v>2</v>
+      </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="2:14">
+    </row>
+    <row r="9" s="1" customFormat="1" spans="2:13">
       <c r="B9" s="8">
         <v>1101</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D9" s="9">
         <v>1</v>
@@ -1447,22 +1578,25 @@
       <c r="E9" s="9">
         <v>104</v>
       </c>
-      <c r="F9" s="3"/>
+      <c r="F9" s="10">
+        <v>2</v>
+      </c>
       <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+      <c r="H9" s="10">
+        <v>1</v>
+      </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="2:14">
+    </row>
+    <row r="10" s="1" customFormat="1" spans="2:13">
       <c r="B10" s="8">
         <v>1102</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D10" s="9">
         <v>1</v>
@@ -1470,22 +1604,25 @@
       <c r="E10" s="9">
         <v>105</v>
       </c>
-      <c r="F10" s="3"/>
+      <c r="F10" s="10">
+        <v>3</v>
+      </c>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="H10" s="10">
+        <v>2</v>
+      </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="2:14">
+    </row>
+    <row r="11" s="1" customFormat="1" spans="2:13">
       <c r="B11" s="8">
         <v>1103</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D11" s="9">
         <v>1</v>
@@ -1493,22 +1630,25 @@
       <c r="E11" s="9">
         <v>106</v>
       </c>
-      <c r="F11" s="3"/>
+      <c r="F11" s="10">
+        <v>4</v>
+      </c>
       <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
+      <c r="H11" s="10">
+        <v>3</v>
+      </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="2:14">
+    </row>
+    <row r="12" s="1" customFormat="1" spans="2:13">
       <c r="B12" s="8">
         <v>1104</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D12" s="9">
         <v>1</v>
@@ -1516,22 +1656,25 @@
       <c r="E12" s="9">
         <v>107</v>
       </c>
-      <c r="F12" s="3"/>
+      <c r="F12" s="10">
+        <v>5</v>
+      </c>
       <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
+      <c r="H12" s="10">
+        <v>4</v>
+      </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="2:14">
+    </row>
+    <row r="13" s="1" customFormat="1" spans="2:13">
       <c r="B13" s="8">
         <v>2001</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D13" s="9">
         <v>2</v>
@@ -1539,22 +1682,25 @@
       <c r="E13" s="9">
         <v>201</v>
       </c>
-      <c r="F13" s="3"/>
+      <c r="F13" s="10">
+        <v>2</v>
+      </c>
       <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
+      <c r="H13" s="10">
+        <v>1</v>
+      </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="2:14">
+    </row>
+    <row r="14" s="1" customFormat="1" spans="2:13">
       <c r="B14" s="8">
         <v>2002</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D14" s="9">
         <v>2</v>
@@ -1562,22 +1708,25 @@
       <c r="E14" s="9">
         <v>201</v>
       </c>
-      <c r="F14" s="3"/>
+      <c r="F14" s="10">
+        <v>3</v>
+      </c>
       <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
+      <c r="H14" s="10">
+        <v>1</v>
+      </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="2:14">
+    </row>
+    <row r="15" s="1" customFormat="1" spans="2:13">
       <c r="B15" s="8">
         <v>2003</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D15" s="9">
         <v>2</v>
@@ -1585,22 +1734,25 @@
       <c r="E15" s="9">
         <v>201</v>
       </c>
-      <c r="F15" s="3"/>
+      <c r="F15" s="10">
+        <v>4</v>
+      </c>
       <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
+      <c r="H15" s="10">
+        <v>2</v>
+      </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="2:14">
+    </row>
+    <row r="16" s="1" customFormat="1" spans="2:13">
       <c r="B16" s="8">
         <v>2011</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D16" s="9">
         <v>2</v>
@@ -1608,22 +1760,25 @@
       <c r="E16" s="9">
         <v>202</v>
       </c>
-      <c r="F16" s="3"/>
+      <c r="F16" s="10">
+        <v>2</v>
+      </c>
       <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
+      <c r="H16" s="10">
+        <v>1</v>
+      </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="2:14">
+    </row>
+    <row r="17" s="1" customFormat="1" spans="2:13">
       <c r="B17" s="8">
         <v>2012</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D17" s="9">
         <v>2</v>
@@ -1631,22 +1786,25 @@
       <c r="E17" s="9">
         <v>202</v>
       </c>
-      <c r="F17" s="3"/>
+      <c r="F17" s="10">
+        <v>4</v>
+      </c>
       <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
+      <c r="H17" s="10">
+        <v>1</v>
+      </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="2:14">
+    </row>
+    <row r="18" s="1" customFormat="1" spans="2:13">
       <c r="B18" s="8">
         <v>2021</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D18" s="9">
         <v>2</v>
@@ -1654,22 +1812,25 @@
       <c r="E18" s="9">
         <v>203</v>
       </c>
-      <c r="F18" s="3"/>
+      <c r="F18" s="10">
+        <v>3</v>
+      </c>
       <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
+      <c r="H18" s="10">
+        <v>1</v>
+      </c>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="2:14">
+    </row>
+    <row r="19" s="1" customFormat="1" spans="2:13">
       <c r="B19" s="8">
         <v>2022</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D19" s="9">
         <v>2</v>
@@ -1677,22 +1838,25 @@
       <c r="E19" s="9">
         <v>203</v>
       </c>
-      <c r="F19" s="3"/>
+      <c r="F19" s="10">
+        <v>5</v>
+      </c>
       <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
+      <c r="H19" s="10">
+        <v>1</v>
+      </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="2:14">
+    </row>
+    <row r="20" s="1" customFormat="1" spans="2:13">
       <c r="B20" s="8">
         <v>2031</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D20" s="9">
         <v>2</v>
@@ -1700,22 +1864,25 @@
       <c r="E20" s="9">
         <v>205</v>
       </c>
-      <c r="F20" s="3"/>
+      <c r="F20" s="10">
+        <v>3</v>
+      </c>
       <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
+      <c r="H20" s="10">
+        <v>1</v>
+      </c>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="2:14">
+    </row>
+    <row r="21" s="1" customFormat="1" spans="2:13">
       <c r="B21" s="8">
         <v>2032</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D21" s="9">
         <v>2</v>
@@ -1723,22 +1890,25 @@
       <c r="E21" s="9">
         <v>205</v>
       </c>
-      <c r="F21" s="3"/>
+      <c r="F21" s="10">
+        <v>3</v>
+      </c>
       <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
+      <c r="H21" s="10">
+        <v>1</v>
+      </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="2:14">
+    </row>
+    <row r="22" s="1" customFormat="1" spans="2:13">
       <c r="B22" s="8">
         <v>2033</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D22" s="9">
         <v>2</v>
@@ -1746,22 +1916,25 @@
       <c r="E22" s="9">
         <v>205</v>
       </c>
-      <c r="F22" s="3"/>
+      <c r="F22" s="10">
+        <v>4</v>
+      </c>
       <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
+      <c r="H22" s="10">
+        <v>1</v>
+      </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="2:14">
+    </row>
+    <row r="23" s="1" customFormat="1" spans="2:13">
       <c r="B23" s="8">
         <v>2101</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D23" s="9">
         <v>2</v>
@@ -1769,22 +1942,25 @@
       <c r="E23" s="9">
         <v>204</v>
       </c>
-      <c r="F23" s="3"/>
+      <c r="F23" s="10">
+        <v>3</v>
+      </c>
       <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
+      <c r="H23" s="10">
+        <v>1</v>
+      </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="2:14">
+    </row>
+    <row r="24" s="1" customFormat="1" spans="2:13">
       <c r="B24" s="8">
         <v>2102</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D24" s="9">
         <v>2</v>
@@ -1792,22 +1968,25 @@
       <c r="E24" s="9">
         <v>204</v>
       </c>
-      <c r="F24" s="3"/>
+      <c r="F24" s="10">
+        <v>3</v>
+      </c>
       <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
+      <c r="H24" s="10">
+        <v>1</v>
+      </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="2:14">
+    </row>
+    <row r="25" s="1" customFormat="1" spans="2:13">
       <c r="B25" s="8">
         <v>2103</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D25" s="9">
         <v>2</v>
@@ -1815,22 +1994,25 @@
       <c r="E25" s="9">
         <v>204</v>
       </c>
-      <c r="F25" s="3"/>
+      <c r="F25" s="10">
+        <v>4</v>
+      </c>
       <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
+      <c r="H25" s="10">
+        <v>1</v>
+      </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="2:14">
+    </row>
+    <row r="26" s="1" customFormat="1" spans="2:13">
       <c r="B26" s="8">
         <v>2104</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D26" s="9">
         <v>2</v>
@@ -1838,22 +2020,25 @@
       <c r="E26" s="9">
         <v>204</v>
       </c>
-      <c r="F26" s="3"/>
+      <c r="F26" s="10">
+        <v>4</v>
+      </c>
       <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
+      <c r="H26" s="10">
+        <v>1</v>
+      </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="2:14">
+    </row>
+    <row r="27" s="1" customFormat="1" spans="2:13">
       <c r="B27" s="8">
         <v>2105</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D27" s="9">
         <v>2</v>
@@ -1861,22 +2046,25 @@
       <c r="E27" s="9">
         <v>204</v>
       </c>
-      <c r="F27" s="3"/>
+      <c r="F27" s="10">
+        <v>5</v>
+      </c>
       <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
+      <c r="H27" s="10">
+        <v>1</v>
+      </c>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="2:14">
+    </row>
+    <row r="28" s="1" customFormat="1" spans="2:13">
       <c r="B28" s="8">
         <v>3001</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D28" s="9">
         <v>3</v>
@@ -1884,22 +2072,25 @@
       <c r="E28" s="9">
         <v>301</v>
       </c>
-      <c r="F28" s="3"/>
+      <c r="F28" s="10">
+        <v>1</v>
+      </c>
       <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
+      <c r="H28" s="10">
+        <v>1</v>
+      </c>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="2:5">
+    </row>
+    <row r="29" s="1" customFormat="1" spans="2:8">
       <c r="B29" s="8">
         <v>3002</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D29" s="9">
         <v>3</v>
@@ -1907,19 +2098,31 @@
       <c r="E29" s="9">
         <v>301</v>
       </c>
-    </row>
-    <row r="30" s="1" customFormat="1" spans="2:5">
+      <c r="F29" s="10">
+        <v>2</v>
+      </c>
+      <c r="H29" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" spans="2:8">
       <c r="B30" s="8">
         <v>3003</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D30" s="9">
         <v>3</v>
       </c>
       <c r="E30" s="9">
         <v>302</v>
+      </c>
+      <c r="F30" s="10">
+        <v>3</v>
+      </c>
+      <c r="H30" s="10">
+        <v>1</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="2:8">
@@ -1927,7 +2130,7 @@
         <v>3004</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D31" s="9">
         <v>3</v>
@@ -1935,14 +2138,20 @@
       <c r="E31" s="9">
         <v>302</v>
       </c>
-      <c r="H31" s="10"/>
+      <c r="F31" s="10">
+        <v>5</v>
+      </c>
+      <c r="G31" s="11"/>
+      <c r="H31" s="10">
+        <v>2</v>
+      </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="2:8">
       <c r="B32" s="8">
         <v>3005</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D32" s="9">
         <v>3</v>
@@ -1950,14 +2159,20 @@
       <c r="E32" s="9">
         <v>303</v>
       </c>
-      <c r="H32" s="10"/>
+      <c r="F32" s="10">
+        <v>4</v>
+      </c>
+      <c r="G32" s="11"/>
+      <c r="H32" s="10">
+        <v>1</v>
+      </c>
     </row>
     <row r="33" s="1" customFormat="1" spans="2:8">
       <c r="B33" s="8">
         <v>4001</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D33" s="9">
         <v>4</v>
@@ -1965,14 +2180,20 @@
       <c r="E33" s="9">
         <v>402</v>
       </c>
-      <c r="H33" s="10"/>
+      <c r="F33" s="10">
+        <v>3</v>
+      </c>
+      <c r="G33" s="11"/>
+      <c r="H33" s="10">
+        <v>1</v>
+      </c>
     </row>
     <row r="34" s="1" customFormat="1" spans="2:8">
       <c r="B34" s="8">
         <v>4002</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D34" s="9">
         <v>4</v>
@@ -1980,14 +2201,20 @@
       <c r="E34" s="9">
         <v>401</v>
       </c>
-      <c r="H34" s="10"/>
+      <c r="F34" s="10">
+        <v>4</v>
+      </c>
+      <c r="G34" s="11"/>
+      <c r="H34" s="10">
+        <v>1</v>
+      </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="2:8">
       <c r="B35" s="8">
         <v>4003</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D35" s="9">
         <v>4</v>
@@ -1995,14 +2222,20 @@
       <c r="E35" s="9">
         <v>403</v>
       </c>
-      <c r="H35" s="10"/>
+      <c r="F35" s="10">
+        <v>5</v>
+      </c>
+      <c r="G35" s="11"/>
+      <c r="H35" s="10">
+        <v>1</v>
+      </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="2:8">
       <c r="B36" s="8">
         <v>4004</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D36" s="9">
         <v>4</v>
@@ -2010,14 +2243,20 @@
       <c r="E36" s="9">
         <v>402</v>
       </c>
-      <c r="H36" s="10"/>
+      <c r="F36" s="10">
+        <v>6</v>
+      </c>
+      <c r="G36" s="11"/>
+      <c r="H36" s="10">
+        <v>1</v>
+      </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="2:8">
       <c r="B37" s="8">
         <v>5001</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D37" s="9">
         <v>5</v>
@@ -2025,14 +2264,20 @@
       <c r="E37" s="9">
         <v>501</v>
       </c>
-      <c r="H37" s="10"/>
+      <c r="F37" s="10">
+        <v>4</v>
+      </c>
+      <c r="G37" s="11"/>
+      <c r="H37" s="10">
+        <v>1</v>
+      </c>
     </row>
     <row r="38" s="1" customFormat="1" spans="2:8">
       <c r="B38" s="8">
         <v>5002</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D38" s="9">
         <v>5</v>
@@ -2040,22 +2285,20 @@
       <c r="E38" s="9">
         <v>501</v>
       </c>
-      <c r="H38" s="10"/>
-    </row>
-    <row r="39" s="1" customFormat="1" spans="2:9">
-      <c r="B39" s="11">
-        <v>5003</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D39" s="1">
+      <c r="F38" s="10">
         <v>5</v>
       </c>
-      <c r="E39" s="1">
-        <v>501</v>
-      </c>
-      <c r="I39" s="10"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" spans="2:8">
+      <c r="B39" s="12"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="H39" s="11"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B30">

--- a/Datas/W-物品配置表.xlsx
+++ b/Datas/W-物品配置表.xlsx
@@ -229,7 +229,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -395,13 +395,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1375,7 +1380,7 @@
         <v>101</v>
       </c>
       <c r="F6" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="8"/>
       <c r="H6" s="7">

--- a/Datas/W-物品配置表.xlsx
+++ b/Datas/W-物品配置表.xlsx
@@ -46,23 +46,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C2" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>中文名
-方便策划维护</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D2" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="H2" authorId="1">
+    <comment ref="I2" authorId="1">
       <text>
         <r>
           <rPr>
@@ -84,7 +68,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I2" authorId="1">
+    <comment ref="J2" authorId="1">
       <text>
         <r>
           <rPr>
@@ -106,7 +90,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J2" authorId="0">
+    <comment ref="K2" authorId="0">
       <text>
         <r>
           <rPr>
@@ -124,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="44">
   <si>
     <t>##comment</t>
   </si>
@@ -132,7 +116,10 @@
     <t>序号</t>
   </si>
   <si>
-    <t>参考中文名</t>
+    <t>物品名称</t>
+  </si>
+  <si>
+    <t>描述</t>
   </si>
   <si>
     <t>物品主类型</t>
@@ -162,6 +149,12 @@
     <t>item_id</t>
   </si>
   <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>des</t>
+  </si>
+  <si>
     <t>item_type</t>
   </si>
   <si>
@@ -189,6 +182,9 @@
     <t>int32</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>EMainType</t>
   </si>
   <si>
@@ -198,15 +194,15 @@
     <t>EQuality</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
     <t>##group</t>
   </si>
   <si>
     <t>c,s</t>
   </si>
   <si>
+    <t>c</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -216,7 +212,34 @@
     <t>破旧铁剑</t>
   </si>
   <si>
-    <t>火属性石·一阶</t>
+    <t>金属性石·一阶·普通</t>
+  </si>
+  <si>
+    <t>一阶普通金属性石。可拖拽到可注灵武器攻击牌上，注入金行之力。拖拽成功后立即消耗。</t>
+  </si>
+  <si>
+    <t>木属性石·一阶·普通</t>
+  </si>
+  <si>
+    <t>一阶普通木属性石。可拖拽到可注灵武器攻击牌上，注入木行之力。拖拽成功后立即消耗。</t>
+  </si>
+  <si>
+    <t>水属性石·一阶·普通</t>
+  </si>
+  <si>
+    <t>一阶普通水属性石。可拖拽到可注灵武器攻击牌上，注入水行之力。拖拽成功后立即消耗。</t>
+  </si>
+  <si>
+    <t>火属性石·一阶·普通</t>
+  </si>
+  <si>
+    <t>一阶普通火属性石。可拖拽到可注灵武器攻击牌上，注入火行之力。拖拽成功后立即消耗。</t>
+  </si>
+  <si>
+    <t>土属性石·一阶·普通</t>
+  </si>
+  <si>
+    <t>一阶普通土属性石。可拖拽到可注灵武器攻击牌上，注入土行之力。拖拽成功后立即消耗。</t>
   </si>
 </sst>
 </file>
@@ -229,7 +252,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -405,11 +428,6 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -426,109 +444,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -737,7 +755,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -761,16 +779,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -779,46 +797,46 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -862,7 +880,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -875,12 +893,26 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1197,26 +1229,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R7"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelRow="6"/>
+  <dimension ref="A1:S13"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="11" style="1"/>
-    <col min="2" max="2" width="20" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="23.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.75" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.375" style="1" customWidth="1"/>
-    <col min="8" max="9" width="14.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.625" style="1" customWidth="1"/>
-    <col min="12" max="16" width="11" style="1"/>
-    <col min="17" max="17" width="12.25" style="1" customWidth="1"/>
-    <col min="18" max="18" width="12.75" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="11" style="1"/>
+    <col min="2" max="2" width="22.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="33.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.375" style="1" customWidth="1"/>
+    <col min="9" max="10" width="14.25" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.625" style="1" customWidth="1"/>
+    <col min="13" max="17" width="11" style="1"/>
+    <col min="18" max="18" width="12.25" style="1" customWidth="1"/>
+    <col min="19" max="19" width="12.75" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:10">
+    <row r="1" s="1" customFormat="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1226,13 +1259,13 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
@@ -1247,103 +1280,123 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:10">
+    <row r="2" s="1" customFormat="1" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="6"/>
+        <v>12</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="D2" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:10">
+    <row r="3" s="1" customFormat="1" spans="1:11">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="6"/>
+        <v>23</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="D3" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>20</v>
-      </c>
       <c r="J3" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:10">
+    <row r="4" s="1" customFormat="1" spans="1:11">
       <c r="A4" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="6"/>
+        <v>29</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="D4" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:10">
+    <row r="5" s="1" customFormat="1" spans="1:11">
       <c r="A5" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B5" s="5"/>
-      <c r="C5" s="6"/>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
       <c r="D5" s="5">
         <v>0</v>
       </c>
@@ -1353,11 +1406,11 @@
       <c r="F5" s="5">
         <v>0</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="5">
+      <c r="G5" s="5">
         <v>0</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
@@ -1365,72 +1418,206 @@
       <c r="J5" s="5">
         <v>0</v>
       </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="2:14">
-      <c r="B6" s="7">
+    <row r="6" s="1" customFormat="1" spans="2:15">
+      <c r="B6" s="6">
         <v>1101</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="7">
-        <v>1</v>
-      </c>
-      <c r="E6" s="7">
+        <v>33</v>
+      </c>
+      <c r="E6" s="6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6">
         <v>101</v>
       </c>
-      <c r="F6" s="7">
-        <v>1</v>
-      </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="7">
-        <v>1</v>
-      </c>
-      <c r="I6" s="7">
+      <c r="G6" s="6">
+        <v>1</v>
+      </c>
+      <c r="H6" s="8"/>
+      <c r="I6" s="6">
+        <v>1</v>
+      </c>
+      <c r="J6" s="6">
         <v>4</v>
       </c>
-      <c r="J6" s="8">
-        <v>1</v>
-      </c>
-      <c r="K6" s="2"/>
+      <c r="K6" s="8">
+        <v>1</v>
+      </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
     </row>
-    <row r="7" s="1" customFormat="1" spans="2:18">
-      <c r="B7" s="7">
-        <v>2101</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="7">
+    <row r="7" s="1" customFormat="1" spans="2:19">
+      <c r="B7" s="9">
+        <v>2112</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="9">
         <v>2</v>
       </c>
-      <c r="E7" s="7">
+      <c r="F7" s="9">
         <v>202</v>
       </c>
-      <c r="F7" s="7">
+      <c r="G7" s="9">
+        <v>1</v>
+      </c>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6">
+        <v>1</v>
+      </c>
+      <c r="J7" s="6">
+        <v>1</v>
+      </c>
+      <c r="K7" s="6">
+        <v>1</v>
+      </c>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="13"/>
+    </row>
+    <row r="8" spans="2:11">
+      <c r="B8" s="9">
+        <v>2122</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="9">
         <v>2</v>
       </c>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7">
-        <v>1</v>
-      </c>
-      <c r="I7" s="7">
-        <v>1</v>
-      </c>
-      <c r="J7" s="7">
-        <v>1</v>
-      </c>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="9"/>
+      <c r="F8" s="9">
+        <v>202</v>
+      </c>
+      <c r="G8" s="9">
+        <v>1</v>
+      </c>
+      <c r="H8" s="12"/>
+      <c r="I8" s="9">
+        <v>1</v>
+      </c>
+      <c r="J8" s="9">
+        <v>1</v>
+      </c>
+      <c r="K8" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11">
+      <c r="B9" s="9">
+        <v>2132</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="9">
+        <v>2</v>
+      </c>
+      <c r="F9" s="9">
+        <v>202</v>
+      </c>
+      <c r="G9" s="9">
+        <v>1</v>
+      </c>
+      <c r="H9" s="12"/>
+      <c r="I9" s="9">
+        <v>1</v>
+      </c>
+      <c r="J9" s="9">
+        <v>1</v>
+      </c>
+      <c r="K9" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11">
+      <c r="B10" s="9">
+        <v>2142</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="9">
+        <v>2</v>
+      </c>
+      <c r="F10" s="9">
+        <v>202</v>
+      </c>
+      <c r="G10" s="9">
+        <v>1</v>
+      </c>
+      <c r="H10" s="12"/>
+      <c r="I10" s="9">
+        <v>1</v>
+      </c>
+      <c r="J10" s="9">
+        <v>1</v>
+      </c>
+      <c r="K10" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11">
+      <c r="B11" s="9">
+        <v>2152</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="9">
+        <v>2</v>
+      </c>
+      <c r="F11" s="9">
+        <v>202</v>
+      </c>
+      <c r="G11" s="9">
+        <v>1</v>
+      </c>
+      <c r="H11" s="12"/>
+      <c r="I11" s="9">
+        <v>1</v>
+      </c>
+      <c r="J11" s="9">
+        <v>1</v>
+      </c>
+      <c r="K11" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="9:11">
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="8"/>
+    </row>
+    <row r="13" spans="11:11">
+      <c r="K13" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
